--- a/party-comparison-updated-v73.xlsx
+++ b/party-comparison-updated-v73.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einat\git_5050\party-comparison\party-comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86627421-A6C9-40E8-B814-97891EB2F0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE6A19F-DE2C-47AB-9C55-7A1AE758316B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="10008" tabRatio="500" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="כל הרשימות" sheetId="1" r:id="rId1"/>
@@ -5093,15 +5093,9 @@
     <t>אחמד טיבי</t>
   </si>
   <si>
-    <t>סאמי אבו שחאדה</t>
-  </si>
-  <si>
     <t>פאתן ג'טאס</t>
   </si>
   <si>
-    <t>בכר עואודה</t>
-  </si>
-  <si>
     <t>עופר כסיף</t>
   </si>
   <si>
@@ -5658,6 +5652,12 @@
   </si>
   <si>
     <t>506</t>
+  </si>
+  <si>
+    <t>עואודה בכר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חסן אלנסאסרה </t>
   </si>
 </sst>
 </file>
@@ -42618,7 +42618,7 @@
         <v>3</v>
       </c>
       <c r="C118" t="s">
-        <v>1657</v>
+        <v>1844</v>
       </c>
       <c r="D118" t="s">
         <v>1488</v>
@@ -42669,7 +42669,7 @@
         <v>6</v>
       </c>
       <c r="C121" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
       <c r="D121" t="s">
         <v>1488</v>
@@ -42686,10 +42686,10 @@
         <v>7</v>
       </c>
       <c r="C122" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="D122" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="E122" t="s">
         <v>1655</v>
@@ -42703,10 +42703,10 @@
         <v>8</v>
       </c>
       <c r="C123" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="D123" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="E123" t="s">
         <v>1655</v>
@@ -42720,10 +42720,10 @@
         <v>9</v>
       </c>
       <c r="C124" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="D124" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="E124" t="s">
         <v>1655</v>
@@ -42737,10 +42737,10 @@
         <v>10</v>
       </c>
       <c r="C125" t="s">
-        <v>1664</v>
+        <v>1845</v>
       </c>
       <c r="D125" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="E125" t="s">
         <v>1655</v>
@@ -42754,13 +42754,13 @@
         <v>1</v>
       </c>
       <c r="C126" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="D126" t="s">
         <v>1488</v>
       </c>
       <c r="E126" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="15" customHeight="1">
@@ -42771,13 +42771,13 @@
         <v>2</v>
       </c>
       <c r="C127" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="D127" t="s">
         <v>1488</v>
       </c>
       <c r="E127" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="15" customHeight="1">
@@ -42788,13 +42788,13 @@
         <v>3</v>
       </c>
       <c r="C128" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="D128" t="s">
         <v>1488</v>
       </c>
       <c r="E128" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="15" customHeight="1">
@@ -42805,13 +42805,13 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="D129" t="s">
         <v>1488</v>
       </c>
       <c r="E129" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="15" customHeight="1">
@@ -42822,13 +42822,13 @@
         <v>5</v>
       </c>
       <c r="C130" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="D130" t="s">
         <v>1488</v>
       </c>
       <c r="E130" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="15" customHeight="1">
@@ -42839,13 +42839,13 @@
         <v>6</v>
       </c>
       <c r="C131" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="D131" t="s">
         <v>1488</v>
       </c>
       <c r="E131" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="15" customHeight="1">
@@ -42856,13 +42856,13 @@
         <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="D132" t="s">
         <v>1488</v>
       </c>
       <c r="E132" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="15" customHeight="1">
@@ -42873,13 +42873,13 @@
         <v>8</v>
       </c>
       <c r="C133" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="D133" t="s">
         <v>1488</v>
       </c>
       <c r="E133" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="15" customHeight="1">
@@ -42890,13 +42890,13 @@
         <v>9</v>
       </c>
       <c r="C134" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="D134" t="s">
         <v>1488</v>
       </c>
       <c r="E134" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="15" customHeight="1">
@@ -42907,13 +42907,13 @@
         <v>1</v>
       </c>
       <c r="C135" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="D135" t="s">
         <v>1488</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" ht="15" customHeight="1">
       <c r="A136" t="s">
         <v>21</v>
       </c>
@@ -42921,7 +42921,7 @@
         <v>2</v>
       </c>
       <c r="C136" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="D136" t="s">
         <v>1488</v>
@@ -42935,7 +42935,7 @@
         <v>3</v>
       </c>
       <c r="C137" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="D137" t="s">
         <v>1487</v>
@@ -42949,7 +42949,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="D138" t="s">
         <v>1487</v>
@@ -42963,7 +42963,7 @@
         <v>5</v>
       </c>
       <c r="C139" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="D139" t="s">
         <v>1488</v>
@@ -42977,7 +42977,7 @@
         <v>6</v>
       </c>
       <c r="C140" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="D140" t="s">
         <v>1488</v>
@@ -42991,7 +42991,7 @@
         <v>7</v>
       </c>
       <c r="C141" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="D141" t="s">
         <v>1488</v>
@@ -43005,7 +43005,7 @@
         <v>8</v>
       </c>
       <c r="C142" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="D142" t="s">
         <v>1487</v>
@@ -43019,7 +43019,7 @@
         <v>9</v>
       </c>
       <c r="C143" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="D143" t="s">
         <v>1487</v>
@@ -43033,7 +43033,7 @@
         <v>10</v>
       </c>
       <c r="C144" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="D144" t="s">
         <v>1487</v>
@@ -43047,7 +43047,7 @@
         <v>11</v>
       </c>
       <c r="C145" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="D145" t="s">
         <v>1487</v>
@@ -43061,7 +43061,7 @@
         <v>12</v>
       </c>
       <c r="C146" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="D146" t="s">
         <v>1488</v>
@@ -43075,7 +43075,7 @@
         <v>13</v>
       </c>
       <c r="C147" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="D147" t="s">
         <v>1488</v>
@@ -43089,7 +43089,7 @@
         <v>14</v>
       </c>
       <c r="C148" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="D148" t="s">
         <v>1487</v>
@@ -43103,7 +43103,7 @@
         <v>15</v>
       </c>
       <c r="C149" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="D149" t="s">
         <v>1487</v>
@@ -43117,7 +43117,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="D150" t="s">
         <v>1487</v>
@@ -43131,7 +43131,7 @@
         <v>17</v>
       </c>
       <c r="C151" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="D151" t="s">
         <v>1488</v>
@@ -43145,7 +43145,7 @@
         <v>18</v>
       </c>
       <c r="C152" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="D152" t="s">
         <v>1488</v>
@@ -43159,7 +43159,7 @@
         <v>19</v>
       </c>
       <c r="C153" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="D153" t="s">
         <v>1487</v>
@@ -43173,7 +43173,7 @@
         <v>20</v>
       </c>
       <c r="C154" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="D154" t="s">
         <v>1488</v>
@@ -43187,7 +43187,7 @@
         <v>21</v>
       </c>
       <c r="C155" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="D155" t="s">
         <v>1487</v>
@@ -43201,7 +43201,7 @@
         <v>22</v>
       </c>
       <c r="C156" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="D156" t="s">
         <v>1488</v>
@@ -43215,7 +43215,7 @@
         <v>23</v>
       </c>
       <c r="C157" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="D157" t="s">
         <v>1488</v>
@@ -43229,7 +43229,7 @@
         <v>24</v>
       </c>
       <c r="C158" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="D158" t="s">
         <v>1487</v>
@@ -43243,7 +43243,7 @@
         <v>25</v>
       </c>
       <c r="C159" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="D159" t="s">
         <v>1487</v>
@@ -43257,7 +43257,7 @@
         <v>26</v>
       </c>
       <c r="C160" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="D160" t="s">
         <v>1488</v>
@@ -43271,7 +43271,7 @@
         <v>27</v>
       </c>
       <c r="C161" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="D161" t="s">
         <v>1488</v>
@@ -43285,7 +43285,7 @@
         <v>28</v>
       </c>
       <c r="C162" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="D162" t="s">
         <v>1487</v>
@@ -43299,7 +43299,7 @@
         <v>29</v>
       </c>
       <c r="C163" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="D163" t="s">
         <v>1488</v>
@@ -43313,7 +43313,7 @@
         <v>30</v>
       </c>
       <c r="C164" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="D164" t="s">
         <v>1487</v>
@@ -43327,7 +43327,7 @@
         <v>31</v>
       </c>
       <c r="C165" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="D165" t="s">
         <v>1488</v>
@@ -43341,7 +43341,7 @@
         <v>32</v>
       </c>
       <c r="C166" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="D166" t="s">
         <v>1487</v>
@@ -43355,7 +43355,7 @@
         <v>33</v>
       </c>
       <c r="C167" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="D167" t="s">
         <v>1488</v>
@@ -43369,7 +43369,7 @@
         <v>34</v>
       </c>
       <c r="C168" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="D168" t="s">
         <v>1487</v>
@@ -43383,7 +43383,7 @@
         <v>35</v>
       </c>
       <c r="C169" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="D169" t="s">
         <v>1488</v>
@@ -43397,7 +43397,7 @@
         <v>36</v>
       </c>
       <c r="C170" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="D170" t="s">
         <v>1487</v>
@@ -43411,7 +43411,7 @@
         <v>37</v>
       </c>
       <c r="C171" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="D171" t="s">
         <v>1488</v>
@@ -43425,7 +43425,7 @@
         <v>38</v>
       </c>
       <c r="C172" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="D172" t="s">
         <v>1487</v>
@@ -43439,7 +43439,7 @@
         <v>39</v>
       </c>
       <c r="C173" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="D173" t="s">
         <v>1488</v>
@@ -43453,7 +43453,7 @@
         <v>40</v>
       </c>
       <c r="C174" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="D174" t="s">
         <v>1488</v>
@@ -43467,13 +43467,13 @@
         <v>1</v>
       </c>
       <c r="C175" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="D175" t="s">
         <v>1488</v>
       </c>
       <c r="E175" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -43484,13 +43484,13 @@
         <v>2</v>
       </c>
       <c r="C176" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="D176" t="s">
         <v>1488</v>
       </c>
       <c r="E176" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -43501,13 +43501,13 @@
         <v>3</v>
       </c>
       <c r="C177" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="D177" t="s">
         <v>1487</v>
       </c>
       <c r="E177" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -43518,13 +43518,13 @@
         <v>4</v>
       </c>
       <c r="C178" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="D178" t="s">
         <v>1488</v>
       </c>
       <c r="E178" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -43535,13 +43535,13 @@
         <v>5</v>
       </c>
       <c r="C179" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="D179" t="s">
         <v>1487</v>
       </c>
       <c r="E179" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -43552,13 +43552,13 @@
         <v>6</v>
       </c>
       <c r="C180" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="D180" t="s">
         <v>1488</v>
       </c>
       <c r="E180" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -43569,13 +43569,13 @@
         <v>7</v>
       </c>
       <c r="C181" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="D181" t="s">
         <v>1488</v>
       </c>
       <c r="E181" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -43586,13 +43586,13 @@
         <v>8</v>
       </c>
       <c r="C182" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="D182" t="s">
         <v>1488</v>
       </c>
       <c r="E182" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -43603,13 +43603,13 @@
         <v>9</v>
       </c>
       <c r="C183" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="D183" t="s">
         <v>1487</v>
       </c>
       <c r="E183" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -43620,13 +43620,13 @@
         <v>10</v>
       </c>
       <c r="C184" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="D184" t="s">
         <v>1488</v>
       </c>
       <c r="E184" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -43637,13 +43637,13 @@
         <v>11</v>
       </c>
       <c r="C185" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="D185" t="s">
         <v>1487</v>
       </c>
       <c r="E185" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -43654,13 +43654,13 @@
         <v>12</v>
       </c>
       <c r="C186" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="D186" t="s">
         <v>1487</v>
       </c>
       <c r="E186" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -43671,13 +43671,13 @@
         <v>13</v>
       </c>
       <c r="C187" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="D187" t="s">
         <v>1488</v>
       </c>
       <c r="E187" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -43688,13 +43688,13 @@
         <v>14</v>
       </c>
       <c r="C188" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="D188" t="s">
         <v>1487</v>
       </c>
       <c r="E188" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -43705,13 +43705,13 @@
         <v>15</v>
       </c>
       <c r="C189" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="D189" t="s">
         <v>1488</v>
       </c>
       <c r="E189" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -43722,13 +43722,13 @@
         <v>16</v>
       </c>
       <c r="C190" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="D190" t="s">
         <v>1487</v>
       </c>
       <c r="E190" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -43739,13 +43739,13 @@
         <v>17</v>
       </c>
       <c r="C191" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="D191" t="s">
         <v>1487</v>
       </c>
       <c r="E191" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -43756,13 +43756,13 @@
         <v>18</v>
       </c>
       <c r="C192" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="D192" t="s">
         <v>1487</v>
       </c>
       <c r="E192" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -43773,13 +43773,13 @@
         <v>19</v>
       </c>
       <c r="C193" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="D193" t="s">
         <v>1487</v>
       </c>
       <c r="E193" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -43790,13 +43790,13 @@
         <v>20</v>
       </c>
       <c r="C194" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="D194" t="s">
         <v>1488</v>
       </c>
       <c r="E194" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -43807,13 +43807,13 @@
         <v>1</v>
       </c>
       <c r="C195" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="D195" t="s">
         <v>1488</v>
       </c>
       <c r="E195" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -43824,13 +43824,13 @@
         <v>2</v>
       </c>
       <c r="C196" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="D196" t="s">
         <v>1487</v>
       </c>
       <c r="E196" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -43841,13 +43841,13 @@
         <v>3</v>
       </c>
       <c r="C197" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="D197" t="s">
         <v>1487</v>
       </c>
       <c r="E197" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -43858,13 +43858,13 @@
         <v>4</v>
       </c>
       <c r="C198" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="D198" t="s">
         <v>1488</v>
       </c>
       <c r="E198" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -43875,13 +43875,13 @@
         <v>5</v>
       </c>
       <c r="C199" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="D199" t="s">
         <v>1487</v>
       </c>
       <c r="E199" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -43909,7 +43909,7 @@
         <v>2</v>
       </c>
       <c r="C201" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="D201" t="s">
         <v>1488</v>
@@ -43926,7 +43926,7 @@
         <v>3</v>
       </c>
       <c r="C202" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="D202" t="s">
         <v>1488</v>
@@ -43943,7 +43943,7 @@
         <v>4</v>
       </c>
       <c r="C203" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="D203" t="s">
         <v>1487</v>
@@ -43960,13 +43960,13 @@
         <v>1</v>
       </c>
       <c r="C204" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="D204" t="s">
         <v>1488</v>
       </c>
       <c r="E204" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -43977,13 +43977,13 @@
         <v>2</v>
       </c>
       <c r="C205" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="D205" t="s">
         <v>1487</v>
       </c>
       <c r="E205" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -43994,13 +43994,13 @@
         <v>3</v>
       </c>
       <c r="C206" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="D206" t="s">
         <v>1488</v>
       </c>
       <c r="E206" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -44011,13 +44011,13 @@
         <v>4</v>
       </c>
       <c r="C207" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="D207" t="s">
         <v>1488</v>
       </c>
       <c r="E207" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -44028,13 +44028,13 @@
         <v>5</v>
       </c>
       <c r="C208" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="D208" t="s">
         <v>1487</v>
       </c>
       <c r="E208" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -44045,13 +44045,13 @@
         <v>6</v>
       </c>
       <c r="C209" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="D209" t="s">
         <v>1488</v>
       </c>
       <c r="E209" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -44062,13 +44062,13 @@
         <v>7</v>
       </c>
       <c r="C210" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="D210" t="s">
         <v>1488</v>
       </c>
       <c r="E210" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -44079,13 +44079,13 @@
         <v>8</v>
       </c>
       <c r="C211" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="D211" t="s">
         <v>1488</v>
       </c>
       <c r="E211" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -44096,13 +44096,13 @@
         <v>9</v>
       </c>
       <c r="C212" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="D212" t="s">
         <v>1488</v>
       </c>
       <c r="E212" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -44113,13 +44113,13 @@
         <v>10</v>
       </c>
       <c r="C213" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="D213" t="s">
         <v>1488</v>
       </c>
       <c r="E213" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -44130,13 +44130,13 @@
         <v>1</v>
       </c>
       <c r="C214" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="D214" t="s">
         <v>1488</v>
       </c>
       <c r="E214" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -44147,13 +44147,13 @@
         <v>2</v>
       </c>
       <c r="C215" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="D215" t="s">
         <v>1488</v>
       </c>
       <c r="E215" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -44164,13 +44164,13 @@
         <v>3</v>
       </c>
       <c r="C216" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="D216" t="s">
         <v>1487</v>
       </c>
       <c r="E216" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -44181,13 +44181,13 @@
         <v>4</v>
       </c>
       <c r="C217" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="D217" t="s">
         <v>1488</v>
       </c>
       <c r="E217" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -44198,13 +44198,13 @@
         <v>5</v>
       </c>
       <c r="C218" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="D218" t="s">
         <v>1487</v>
       </c>
       <c r="E218" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -44215,13 +44215,13 @@
         <v>6</v>
       </c>
       <c r="C219" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="D219" t="s">
         <v>1487</v>
       </c>
       <c r="E219" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -44232,13 +44232,13 @@
         <v>7</v>
       </c>
       <c r="C220" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="D220" t="s">
         <v>1488</v>
       </c>
       <c r="E220" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -44249,13 +44249,13 @@
         <v>8</v>
       </c>
       <c r="C221" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="D221" t="s">
         <v>1488</v>
       </c>
       <c r="E221" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -44266,13 +44266,13 @@
         <v>9</v>
       </c>
       <c r="C222" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="D222" t="s">
         <v>1488</v>
       </c>
       <c r="E222" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -44283,13 +44283,13 @@
         <v>10</v>
       </c>
       <c r="C223" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="D223" t="s">
         <v>1488</v>
       </c>
       <c r="E223" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -44300,13 +44300,13 @@
         <v>11</v>
       </c>
       <c r="C224" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="D224" t="s">
         <v>1487</v>
       </c>
       <c r="E224" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -44317,13 +44317,13 @@
         <v>1</v>
       </c>
       <c r="C225" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="D225" t="s">
         <v>1488</v>
       </c>
       <c r="E225" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -44334,13 +44334,13 @@
         <v>2</v>
       </c>
       <c r="C226" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="D226" t="s">
         <v>1488</v>
       </c>
       <c r="E226" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -44351,13 +44351,13 @@
         <v>3</v>
       </c>
       <c r="C227" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="D227" t="s">
         <v>1488</v>
       </c>
       <c r="E227" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -44368,13 +44368,13 @@
         <v>4</v>
       </c>
       <c r="C228" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="D228" t="s">
         <v>1488</v>
       </c>
       <c r="E228" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -44385,13 +44385,13 @@
         <v>5</v>
       </c>
       <c r="C229" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="D229" t="s">
         <v>1487</v>
       </c>
       <c r="E229" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -44402,13 +44402,13 @@
         <v>6</v>
       </c>
       <c r="C230" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="D230" t="s">
         <v>1488</v>
       </c>
       <c r="E230" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -44419,13 +44419,13 @@
         <v>1</v>
       </c>
       <c r="C231" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="D231" t="s">
         <v>1488</v>
       </c>
       <c r="E231" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -44436,13 +44436,13 @@
         <v>2</v>
       </c>
       <c r="C232" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="D232" t="s">
         <v>1488</v>
       </c>
       <c r="E232" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -44453,13 +44453,13 @@
         <v>3</v>
       </c>
       <c r="C233" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="D233" t="s">
         <v>1488</v>
       </c>
       <c r="E233" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -44470,13 +44470,13 @@
         <v>4</v>
       </c>
       <c r="C234" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="D234" t="s">
         <v>1488</v>
       </c>
       <c r="E234" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -44487,13 +44487,13 @@
         <v>5</v>
       </c>
       <c r="C235" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D235" t="s">
         <v>1488</v>
       </c>
       <c r="E235" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -44504,13 +44504,13 @@
         <v>6</v>
       </c>
       <c r="C236" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="D236" t="s">
         <v>1488</v>
       </c>
       <c r="E236" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -44521,13 +44521,13 @@
         <v>7</v>
       </c>
       <c r="C237" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="D237" t="s">
         <v>1488</v>
       </c>
       <c r="E237" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -44538,13 +44538,13 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="D238" t="s">
         <v>1488</v>
       </c>
       <c r="E238" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
     </row>
   </sheetData>
@@ -44576,7 +44576,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>4</v>
@@ -44588,16 +44588,16 @@
         <v>6</v>
       </c>
       <c r="F1" s="10" t="s">
+        <v>1798</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1799</v>
+      </c>
+      <c r="H1" t="s">
         <v>1800</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>1801</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1802</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1803</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1">
@@ -44621,7 +44621,7 @@
         <v>0.13636363636363635</v>
       </c>
       <c r="F2" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="G2">
         <v>32</v>
@@ -44655,7 +44655,7 @@
         <v>0.5</v>
       </c>
       <c r="F3" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -44689,7 +44689,7 @@
         <v>0.5</v>
       </c>
       <c r="F4" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="G4">
         <v>24</v>
@@ -44723,7 +44723,7 @@
         <v>0.44444444444444442</v>
       </c>
       <c r="F5" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -44757,7 +44757,7 @@
         <v>0.25</v>
       </c>
       <c r="F6" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -44791,7 +44791,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="G7">
         <v>11</v>
@@ -44825,7 +44825,7 @@
         <v>0.25</v>
       </c>
       <c r="F8" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="G8">
         <v>6</v>
@@ -44859,7 +44859,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="G9">
         <v>7</v>
@@ -44893,7 +44893,7 @@
         <v>0.125</v>
       </c>
       <c r="F10" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -44927,7 +44927,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="F11" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="G11">
         <v>7</v>
@@ -44961,7 +44961,7 @@
         <v>0.2</v>
       </c>
       <c r="F12" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -44995,7 +44995,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="G13">
         <v>8</v>
@@ -45029,7 +45029,7 @@
         <v>0.25</v>
       </c>
       <c r="F14" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -45063,7 +45063,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -45097,7 +45097,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -45112,7 +45112,7 @@
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
       <c r="A17" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="B17">
         <f>SUM(B2:B15)</f>
@@ -45163,10 +45163,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="D1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="E1" t="s">
         <v>10</v>
@@ -45219,13 +45219,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D2" t="s">
         <v>1822</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1823</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1824</v>
       </c>
       <c r="E2">
         <v>20</v>
@@ -45278,13 +45278,13 @@
         <v>24</v>
       </c>
       <c r="B3" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D3" t="s">
         <v>1825</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1826</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1827</v>
       </c>
       <c r="E3">
         <v>21</v>
@@ -45337,13 +45337,13 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C4" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="D4" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="E4">
         <v>26</v>
@@ -45396,13 +45396,13 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C5" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="D5" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="E5">
         <v>20</v>
@@ -45455,13 +45455,13 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D6" t="s">
         <v>1832</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1833</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1834</v>
       </c>
       <c r="E6">
         <v>20</v>
@@ -45514,13 +45514,13 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="C7" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="D7" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="E7">
         <v>31</v>
@@ -45573,13 +45573,13 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="C8" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="D8" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="E8">
         <v>21</v>
@@ -45632,13 +45632,13 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D9" t="s">
         <v>1839</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1840</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1841</v>
       </c>
       <c r="E9">
         <v>21</v>
@@ -45691,13 +45691,13 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="C10" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="D10" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="E10">
         <v>21</v>
@@ -45750,13 +45750,13 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="C11" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="D11" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="E11">
         <v>21</v>
@@ -46004,15 +46004,15 @@
       </c>
       <c r="E6">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C6,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D6)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C6,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D6)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="H6">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C6)</f>
@@ -47012,15 +47012,15 @@
       </c>
       <c r="E34">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C34,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D34)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C34,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D34)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G34">
         <f t="shared" ref="G34:G65" si="2">IF($D34=0,0,$E34/$D34)</f>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="H34">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C34)</f>
@@ -47516,15 +47516,15 @@
       </c>
       <c r="E48">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C48,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D48)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C48,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D48)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G48">
         <f t="shared" si="2"/>
-        <v>0.1111111111111111</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="H48">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C48)</f>
@@ -48020,15 +48020,15 @@
       </c>
       <c r="E62">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C62,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D62)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C62,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D62)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G62">
         <f t="shared" si="2"/>
-        <v>0.1111111111111111</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="H62">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C62)</f>
@@ -48524,15 +48524,15 @@
       </c>
       <c r="E76">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C76,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D76)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C76,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D76)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="H76">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C76)</f>
@@ -49028,15 +49028,15 @@
       </c>
       <c r="E90">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C90,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D90)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C90,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D90)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G90">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="H90">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C90)</f>
@@ -50540,15 +50540,15 @@
       </c>
       <c r="E132">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C132,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D132)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C132,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D132)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G132">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="H132">
         <f>COUNTIFS('מועמדים 2026'!$A:$A,$C132)</f>
